--- a/data/nzd0246/nzd0246.xlsx
+++ b/data/nzd0246/nzd0246.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q332"/>
+  <dimension ref="A1:Q334"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19357,6 +19357,120 @@
         </is>
       </c>
     </row>
+    <row r="333">
+      <c r="A333" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-20 22:05:55+00:00</t>
+        </is>
+      </c>
+      <c r="B333" t="n">
+        <v>337.03</v>
+      </c>
+      <c r="C333" t="n">
+        <v>346.92</v>
+      </c>
+      <c r="D333" t="n">
+        <v>368.5</v>
+      </c>
+      <c r="E333" t="n">
+        <v>365.68</v>
+      </c>
+      <c r="F333" t="n">
+        <v>365.31</v>
+      </c>
+      <c r="G333" t="n">
+        <v>362.85</v>
+      </c>
+      <c r="H333" t="n">
+        <v>378.43</v>
+      </c>
+      <c r="I333" t="n">
+        <v>371.39</v>
+      </c>
+      <c r="J333" t="n">
+        <v>366.4</v>
+      </c>
+      <c r="K333" t="n">
+        <v>357.32</v>
+      </c>
+      <c r="L333" t="n">
+        <v>360.01</v>
+      </c>
+      <c r="M333" t="n">
+        <v>368.49</v>
+      </c>
+      <c r="N333" t="n">
+        <v>375.09</v>
+      </c>
+      <c r="O333" t="n">
+        <v>374.71</v>
+      </c>
+      <c r="P333" t="n">
+        <v>389.23</v>
+      </c>
+      <c r="Q333" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-28 22:06:12+00:00</t>
+        </is>
+      </c>
+      <c r="B334" t="n">
+        <v>338.08</v>
+      </c>
+      <c r="C334" t="n">
+        <v>347.93</v>
+      </c>
+      <c r="D334" t="n">
+        <v>369.65</v>
+      </c>
+      <c r="E334" t="n">
+        <v>366.35</v>
+      </c>
+      <c r="F334" t="n">
+        <v>366.26</v>
+      </c>
+      <c r="G334" t="n">
+        <v>363.01</v>
+      </c>
+      <c r="H334" t="n">
+        <v>378.57</v>
+      </c>
+      <c r="I334" t="n">
+        <v>371.95</v>
+      </c>
+      <c r="J334" t="n">
+        <v>366.46</v>
+      </c>
+      <c r="K334" t="n">
+        <v>357.58</v>
+      </c>
+      <c r="L334" t="n">
+        <v>360.18</v>
+      </c>
+      <c r="M334" t="n">
+        <v>368.15</v>
+      </c>
+      <c r="N334" t="n">
+        <v>374.36</v>
+      </c>
+      <c r="O334" t="n">
+        <v>374.82</v>
+      </c>
+      <c r="P334" t="n">
+        <v>389.23</v>
+      </c>
+      <c r="Q334" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -19368,7 +19482,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B341"/>
+  <dimension ref="A1:B343"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22781,6 +22895,26 @@
       </c>
       <c r="B341" t="n">
         <v>-0.77</v>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="inlineStr">
+        <is>
+          <t>2026-07-20 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B342" t="n">
+        <v>-0.75</v>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="inlineStr">
+        <is>
+          <t>2026-07-28 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B343" t="n">
+        <v>0.99</v>
       </c>
     </row>
   </sheetData>
@@ -22949,28 +23083,28 @@
         <v>0.1147</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.05874319267540035</v>
+        <v>-0.06330687394547117</v>
       </c>
       <c r="J2" t="n">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="K2" t="n">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="L2" t="n">
-        <v>0.004051222176571501</v>
+        <v>0.00475548483668542</v>
       </c>
       <c r="M2" t="n">
-        <v>5.324728575802709</v>
+        <v>5.317191031522134</v>
       </c>
       <c r="N2" t="n">
-        <v>50.061033747911</v>
+        <v>49.85488045511882</v>
       </c>
       <c r="O2" t="n">
-        <v>7.075382233343369</v>
+        <v>7.060798853891734</v>
       </c>
       <c r="P2" t="n">
-        <v>343.1080289438642</v>
+        <v>343.1555569141676</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -23027,28 +23161,28 @@
         <v>0.1303</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.08739854507615911</v>
+        <v>-0.09135359991096256</v>
       </c>
       <c r="J3" t="n">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="K3" t="n">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="L3" t="n">
-        <v>0.01369357704223673</v>
+        <v>0.01510542070239296</v>
       </c>
       <c r="M3" t="n">
-        <v>4.536239769034476</v>
+        <v>4.531306221741993</v>
       </c>
       <c r="N3" t="n">
-        <v>32.46662436688946</v>
+        <v>32.34291829643163</v>
       </c>
       <c r="O3" t="n">
-        <v>5.697949136916673</v>
+        <v>5.687083461356237</v>
       </c>
       <c r="P3" t="n">
-        <v>353.228708746418</v>
+        <v>353.2698979408933</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -23105,28 +23239,28 @@
         <v>0.0901</v>
       </c>
       <c r="I4" t="n">
-        <v>0.04980318548869531</v>
+        <v>0.04517901435542112</v>
       </c>
       <c r="J4" t="n">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="K4" t="n">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="L4" t="n">
-        <v>0.004467090996489786</v>
+        <v>0.003716746284618266</v>
       </c>
       <c r="M4" t="n">
-        <v>4.280669141242288</v>
+        <v>4.281512789741672</v>
       </c>
       <c r="N4" t="n">
-        <v>32.6196159686384</v>
+        <v>32.52103570457371</v>
       </c>
       <c r="O4" t="n">
-        <v>5.711358504650045</v>
+        <v>5.702721780393438</v>
       </c>
       <c r="P4" t="n">
-        <v>371.7505825299667</v>
+        <v>371.798740209155</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -23183,28 +23317,28 @@
         <v>0.1128</v>
       </c>
       <c r="I5" t="n">
-        <v>0.03498652293224989</v>
+        <v>0.03284901327450002</v>
       </c>
       <c r="J5" t="n">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="K5" t="n">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="L5" t="n">
-        <v>0.002968718967266359</v>
+        <v>0.002650641137175391</v>
       </c>
       <c r="M5" t="n">
-        <v>3.363055170848903</v>
+        <v>3.356050797083426</v>
       </c>
       <c r="N5" t="n">
-        <v>24.02970702734039</v>
+        <v>23.90572113184576</v>
       </c>
       <c r="O5" t="n">
-        <v>4.902010508693387</v>
+        <v>4.889347720488466</v>
       </c>
       <c r="P5" t="n">
-        <v>366.9131616435712</v>
+        <v>366.9355818644965</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -23261,28 +23395,28 @@
         <v>0.09660000000000001</v>
       </c>
       <c r="I6" t="n">
-        <v>0.06010525095589633</v>
+        <v>0.06130135696240931</v>
       </c>
       <c r="J6" t="n">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="K6" t="n">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="L6" t="n">
-        <v>0.007309874039520659</v>
+        <v>0.007700444019181907</v>
       </c>
       <c r="M6" t="n">
-        <v>3.901308521568961</v>
+        <v>3.884347165631132</v>
       </c>
       <c r="N6" t="n">
-        <v>28.67714094954007</v>
+        <v>28.51202203502652</v>
       </c>
       <c r="O6" t="n">
-        <v>5.355104195955488</v>
+        <v>5.339664974043457</v>
       </c>
       <c r="P6" t="n">
-        <v>363.1318962791923</v>
+        <v>363.1193465396404</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -23339,28 +23473,28 @@
         <v>0.1426</v>
       </c>
       <c r="I7" t="n">
-        <v>0.07396784262330953</v>
+        <v>0.07864754844866002</v>
       </c>
       <c r="J7" t="n">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="K7" t="n">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="L7" t="n">
-        <v>0.01410275442092745</v>
+        <v>0.01605561218947249</v>
       </c>
       <c r="M7" t="n">
-        <v>3.700981631004157</v>
+        <v>3.701418888313259</v>
       </c>
       <c r="N7" t="n">
-        <v>22.35737579624922</v>
+        <v>22.31900735396237</v>
       </c>
       <c r="O7" t="n">
-        <v>4.728358678891568</v>
+        <v>4.724299668094983</v>
       </c>
       <c r="P7" t="n">
-        <v>356.8936015883518</v>
+        <v>356.8445116681855</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -23417,28 +23551,28 @@
         <v>0.0623</v>
       </c>
       <c r="I8" t="n">
-        <v>0.08966384190908946</v>
+        <v>0.09598178388925892</v>
       </c>
       <c r="J8" t="n">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="K8" t="n">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="L8" t="n">
-        <v>0.01512340290171821</v>
+        <v>0.01742037777784944</v>
       </c>
       <c r="M8" t="n">
-        <v>4.104810176185743</v>
+        <v>4.116985056475394</v>
       </c>
       <c r="N8" t="n">
-        <v>30.6037182632318</v>
+        <v>30.59487136123169</v>
       </c>
       <c r="O8" t="n">
-        <v>5.532062749393918</v>
+        <v>5.5312630891354</v>
       </c>
       <c r="P8" t="n">
-        <v>370.6304286691799</v>
+        <v>370.5641539447457</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -23495,28 +23629,28 @@
         <v>0.0648</v>
       </c>
       <c r="I9" t="n">
-        <v>0.1433825615095565</v>
+        <v>0.1451910665676912</v>
       </c>
       <c r="J9" t="n">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="K9" t="n">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="L9" t="n">
-        <v>0.04198596687903644</v>
+        <v>0.04353416373236219</v>
       </c>
       <c r="M9" t="n">
-        <v>4.026169326833783</v>
+        <v>4.010390453454042</v>
       </c>
       <c r="N9" t="n">
-        <v>27.42000906618604</v>
+        <v>27.26966857230463</v>
       </c>
       <c r="O9" t="n">
-        <v>5.236411850321367</v>
+        <v>5.222036822189655</v>
       </c>
       <c r="P9" t="n">
-        <v>366.2405122886248</v>
+        <v>366.2215397073676</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -23573,28 +23707,28 @@
         <v>0.08</v>
       </c>
       <c r="I10" t="n">
-        <v>0.1735756003024285</v>
+        <v>0.1772826519433682</v>
       </c>
       <c r="J10" t="n">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="K10" t="n">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="L10" t="n">
-        <v>0.07109300218068804</v>
+        <v>0.07466876495860064</v>
       </c>
       <c r="M10" t="n">
-        <v>3.543321262534588</v>
+        <v>3.540013970654657</v>
       </c>
       <c r="N10" t="n">
-        <v>23.01070605877246</v>
+        <v>22.93250760261962</v>
       </c>
       <c r="O10" t="n">
-        <v>4.796947577238307</v>
+        <v>4.788789784759779</v>
       </c>
       <c r="P10" t="n">
-        <v>358.5400973164423</v>
+        <v>358.5012106977479</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -23651,28 +23785,28 @@
         <v>0.0946</v>
       </c>
       <c r="I11" t="n">
-        <v>0.2680995464522095</v>
+        <v>0.2707562906857534</v>
       </c>
       <c r="J11" t="n">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="K11" t="n">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="L11" t="n">
-        <v>0.134296122638413</v>
+        <v>0.1380447046093334</v>
       </c>
       <c r="M11" t="n">
-        <v>4.213705574542473</v>
+        <v>4.200666761853856</v>
       </c>
       <c r="N11" t="n">
-        <v>27.083529460222</v>
+        <v>26.95149834315636</v>
       </c>
       <c r="O11" t="n">
-        <v>5.204183841893174</v>
+        <v>5.191483250782608</v>
       </c>
       <c r="P11" t="n">
-        <v>347.9166033665022</v>
+        <v>347.888733764586</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -23729,28 +23863,28 @@
         <v>0.0968</v>
       </c>
       <c r="I12" t="n">
-        <v>0.3129141429752013</v>
+        <v>0.3181747550819841</v>
       </c>
       <c r="J12" t="n">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="K12" t="n">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="L12" t="n">
-        <v>0.1600684163771605</v>
+        <v>0.1658762075858097</v>
       </c>
       <c r="M12" t="n">
-        <v>4.379552941938392</v>
+        <v>4.375474761147429</v>
       </c>
       <c r="N12" t="n">
-        <v>30.03280262323495</v>
+        <v>29.97358301214519</v>
       </c>
       <c r="O12" t="n">
-        <v>5.480219213063922</v>
+        <v>5.474813513914897</v>
       </c>
       <c r="P12" t="n">
-        <v>347.1013456028243</v>
+        <v>347.0461620556675</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -23807,28 +23941,28 @@
         <v>0.1069</v>
       </c>
       <c r="I13" t="n">
-        <v>0.3064788644599081</v>
+        <v>0.3129547949713758</v>
       </c>
       <c r="J13" t="n">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="K13" t="n">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="L13" t="n">
-        <v>0.1781223534351486</v>
+        <v>0.1852311334090985</v>
       </c>
       <c r="M13" t="n">
-        <v>3.971014037652846</v>
+        <v>3.977742050437891</v>
       </c>
       <c r="N13" t="n">
-        <v>25.33360626729601</v>
+        <v>25.36556113935818</v>
       </c>
       <c r="O13" t="n">
-        <v>5.033250070014007</v>
+        <v>5.036423447185332</v>
       </c>
       <c r="P13" t="n">
-        <v>354.4489664014689</v>
+        <v>354.3810358197521</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -23885,28 +24019,28 @@
         <v>0.1045</v>
       </c>
       <c r="I14" t="n">
-        <v>0.2567345865149037</v>
+        <v>0.2629213959738328</v>
       </c>
       <c r="J14" t="n">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="K14" t="n">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="L14" t="n">
-        <v>0.1432962955118166</v>
+        <v>0.1499989776370163</v>
       </c>
       <c r="M14" t="n">
-        <v>3.65810465110583</v>
+        <v>3.664952894901113</v>
       </c>
       <c r="N14" t="n">
-        <v>23.03412149868259</v>
+        <v>23.06448812781466</v>
       </c>
       <c r="O14" t="n">
-        <v>4.799387617048929</v>
+        <v>4.802550169213712</v>
       </c>
       <c r="P14" t="n">
-        <v>362.4511628143619</v>
+        <v>362.3862662147735</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -23963,28 +24097,28 @@
         <v>0.07290000000000001</v>
       </c>
       <c r="I15" t="n">
-        <v>0.1818512551173853</v>
+        <v>0.1909591781130116</v>
       </c>
       <c r="J15" t="n">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="K15" t="n">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="L15" t="n">
-        <v>0.06423572413604339</v>
+        <v>0.07039059311781815</v>
       </c>
       <c r="M15" t="n">
-        <v>4.069359726876917</v>
+        <v>4.088727817755822</v>
       </c>
       <c r="N15" t="n">
-        <v>28.15980580030781</v>
+        <v>28.35487724197559</v>
       </c>
       <c r="O15" t="n">
-        <v>5.306581366596371</v>
+        <v>5.324929787516037</v>
       </c>
       <c r="P15" t="n">
-        <v>361.9973682664094</v>
+        <v>361.9018271552758</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -24041,28 +24175,28 @@
         <v>0.2</v>
       </c>
       <c r="I16" t="n">
-        <v>1.196040003479847</v>
+        <v>1.207673789430289</v>
       </c>
       <c r="J16" t="n">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="K16" t="n">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="L16" t="n">
-        <v>0.3615751490075143</v>
+        <v>0.3681969078083659</v>
       </c>
       <c r="M16" t="n">
-        <v>9.708091714476589</v>
+        <v>9.722138826710122</v>
       </c>
       <c r="N16" t="n">
-        <v>148.3541836077816</v>
+        <v>148.0544229237079</v>
       </c>
       <c r="O16" t="n">
-        <v>12.18007321849017</v>
+        <v>12.16776162339269</v>
       </c>
       <c r="P16" t="n">
-        <v>346.875253803379</v>
+        <v>346.7533696716071</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -24100,7 +24234,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q332"/>
+  <dimension ref="A1:Q334"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -52931,6 +53065,180 @@
         </is>
       </c>
     </row>
+    <row r="333">
+      <c r="A333" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-20 22:05:55+00:00</t>
+        </is>
+      </c>
+      <c r="B333" t="inlineStr">
+        <is>
+          <t>-38.1239384043597,174.73341893775617</t>
+        </is>
+      </c>
+      <c r="C333" t="inlineStr">
+        <is>
+          <t>-38.123649905859686,174.73424535245653</t>
+        </is>
+      </c>
+      <c r="D333" t="inlineStr">
+        <is>
+          <t>-38.123271362828646,174.73500769485676</t>
+        </is>
+      </c>
+      <c r="E333" t="inlineStr">
+        <is>
+          <t>-38.12284850401782,174.73567957515894</t>
+        </is>
+      </c>
+      <c r="F333" t="inlineStr">
+        <is>
+          <t>-38.12236549779273,174.73633229266903</t>
+        </is>
+      </c>
+      <c r="G333" t="inlineStr">
+        <is>
+          <t>-38.121894518429954,174.73700309361627</t>
+        </is>
+      </c>
+      <c r="H333" t="inlineStr">
+        <is>
+          <t>-38.12130774477024,174.73753134228906</t>
+        </is>
+      </c>
+      <c r="I333" t="inlineStr">
+        <is>
+          <t>-38.12086734665122,174.738239677947</t>
+        </is>
+      </c>
+      <c r="J333" t="inlineStr">
+        <is>
+          <t>-38.1204130946829,174.7389323227239</t>
+        </is>
+      </c>
+      <c r="K333" t="inlineStr">
+        <is>
+          <t>-38.11999636903229,174.73966763497</t>
+        </is>
+      </c>
+      <c r="L333" t="inlineStr">
+        <is>
+          <t>-38.11951287390231,174.7403231101372</t>
+        </is>
+      </c>
+      <c r="M333" t="inlineStr">
+        <is>
+          <t>-38.11899324780892,174.74093169403494</t>
+        </is>
+      </c>
+      <c r="N333" t="inlineStr">
+        <is>
+          <t>-38.118459865148715,174.7415042316515</t>
+        </is>
+      </c>
+      <c r="O333" t="inlineStr">
+        <is>
+          <t>-38.11793405893776,174.74209424143285</t>
+        </is>
+      </c>
+      <c r="P333" t="inlineStr">
+        <is>
+          <t>-38.11731696371281,174.74255897824276</t>
+        </is>
+      </c>
+      <c r="Q333" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-28 22:06:12+00:00</t>
+        </is>
+      </c>
+      <c r="B334" t="inlineStr">
+        <is>
+          <t>-38.12392937965904,174.73341534415542</t>
+        </is>
+      </c>
+      <c r="C334" t="inlineStr">
+        <is>
+          <t>-38.12364122497447,174.7342418957076</t>
+        </is>
+      </c>
+      <c r="D334" t="inlineStr">
+        <is>
+          <t>-38.123262342174804,174.73500124112627</t>
+        </is>
+      </c>
+      <c r="E334" t="inlineStr">
+        <is>
+          <t>-38.122844085424866,174.73567436830064</t>
+        </is>
+      </c>
+      <c r="F334" t="inlineStr">
+        <is>
+          <t>-38.12235937016096,174.73632472714834</t>
+        </is>
+      </c>
+      <c r="G334" t="inlineStr">
+        <is>
+          <t>-38.12189348568589,174.73700182036947</t>
+        </is>
+      </c>
+      <c r="H334" t="inlineStr">
+        <is>
+          <t>-38.12130684029652,174.73753022927755</t>
+        </is>
+      </c>
+      <c r="I334" t="inlineStr">
+        <is>
+          <t>-38.120863728014825,174.73823522689537</t>
+        </is>
+      </c>
+      <c r="J334" t="inlineStr">
+        <is>
+          <t>-38.12041270335279,174.7389318505889</t>
+        </is>
+      </c>
+      <c r="K334" t="inlineStr">
+        <is>
+          <t>-38.119994641904185,174.73966563154454</t>
+        </is>
+      </c>
+      <c r="L334" t="inlineStr">
+        <is>
+          <t>-38.119511734389505,174.7403218144964</t>
+        </is>
+      </c>
+      <c r="M334" t="inlineStr">
+        <is>
+          <t>-38.11899545714938,174.74093438025585</t>
+        </is>
+      </c>
+      <c r="N334" t="inlineStr">
+        <is>
+          <t>-38.118464292335105,174.74151038894917</t>
+        </is>
+      </c>
+      <c r="O334" t="inlineStr">
+        <is>
+          <t>-38.11793341680786,174.74209328580585</t>
+        </is>
+      </c>
+      <c r="P334" t="inlineStr">
+        <is>
+          <t>-38.11731696371281,174.74255897824276</t>
+        </is>
+      </c>
+      <c r="Q334" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0246/nzd0246.xlsx
+++ b/data/nzd0246/nzd0246.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q334"/>
+  <dimension ref="A1:Q335"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19471,6 +19471,63 @@
         </is>
       </c>
     </row>
+    <row r="335">
+      <c r="A335" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-05 22:06:04+00:00</t>
+        </is>
+      </c>
+      <c r="B335" t="n">
+        <v>338.46</v>
+      </c>
+      <c r="C335" t="n">
+        <v>348.37</v>
+      </c>
+      <c r="D335" t="n">
+        <v>370.21</v>
+      </c>
+      <c r="E335" t="n">
+        <v>366.66</v>
+      </c>
+      <c r="F335" t="n">
+        <v>366</v>
+      </c>
+      <c r="G335" t="n">
+        <v>362.89</v>
+      </c>
+      <c r="H335" t="n">
+        <v>380.76</v>
+      </c>
+      <c r="I335" t="n">
+        <v>373.81</v>
+      </c>
+      <c r="J335" t="n">
+        <v>368.06</v>
+      </c>
+      <c r="K335" t="n">
+        <v>358.02</v>
+      </c>
+      <c r="L335" t="n">
+        <v>360.16</v>
+      </c>
+      <c r="M335" t="n">
+        <v>367.68</v>
+      </c>
+      <c r="N335" t="n">
+        <v>374.21</v>
+      </c>
+      <c r="O335" t="n">
+        <v>373.32</v>
+      </c>
+      <c r="P335" t="n">
+        <v>389.23</v>
+      </c>
+      <c r="Q335" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -19482,7 +19539,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B343"/>
+  <dimension ref="A1:B344"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22915,6 +22972,16 @@
       </c>
       <c r="B343" t="n">
         <v>0.99</v>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="inlineStr">
+        <is>
+          <t>2026-08-05 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B344" t="n">
+        <v>-0.8100000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -23083,28 +23150,28 @@
         <v>0.1147</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.06330687394547117</v>
+        <v>-0.06501033698183308</v>
       </c>
       <c r="J2" t="n">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="K2" t="n">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="L2" t="n">
-        <v>0.00475548483668542</v>
+        <v>0.005043601596489089</v>
       </c>
       <c r="M2" t="n">
-        <v>5.317191031522134</v>
+        <v>5.310443553997287</v>
       </c>
       <c r="N2" t="n">
-        <v>49.85488045511882</v>
+        <v>49.73200499994834</v>
       </c>
       <c r="O2" t="n">
-        <v>7.060798853891734</v>
+        <v>7.052092242728277</v>
       </c>
       <c r="P2" t="n">
-        <v>343.1555569141676</v>
+        <v>343.1733242041016</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -23161,28 +23228,28 @@
         <v>0.1303</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.09135359991096256</v>
+        <v>-0.09273925602173418</v>
       </c>
       <c r="J3" t="n">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="K3" t="n">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="L3" t="n">
-        <v>0.01510542070239296</v>
+        <v>0.01565206419336007</v>
       </c>
       <c r="M3" t="n">
-        <v>4.531306221741993</v>
+        <v>4.525512194295319</v>
       </c>
       <c r="N3" t="n">
-        <v>32.34291829643163</v>
+        <v>32.26354527857175</v>
       </c>
       <c r="O3" t="n">
-        <v>5.687083461356237</v>
+        <v>5.680100815880977</v>
       </c>
       <c r="P3" t="n">
-        <v>353.2698979408933</v>
+        <v>353.2843504727905</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -23239,28 +23306,28 @@
         <v>0.0901</v>
       </c>
       <c r="I4" t="n">
-        <v>0.04517901435542112</v>
+        <v>0.04357583127361371</v>
       </c>
       <c r="J4" t="n">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="K4" t="n">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="L4" t="n">
-        <v>0.003716746284618266</v>
+        <v>0.003478649821405444</v>
       </c>
       <c r="M4" t="n">
-        <v>4.281512789741672</v>
+        <v>4.277845499619207</v>
       </c>
       <c r="N4" t="n">
-        <v>32.52103570457371</v>
+        <v>32.44704229904371</v>
       </c>
       <c r="O4" t="n">
-        <v>5.702721780393438</v>
+        <v>5.696230534225569</v>
       </c>
       <c r="P4" t="n">
-        <v>371.798740209155</v>
+        <v>371.815461569128</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -23317,28 +23384,28 @@
         <v>0.1128</v>
       </c>
       <c r="I5" t="n">
-        <v>0.03284901327450002</v>
+        <v>0.03217678452215789</v>
       </c>
       <c r="J5" t="n">
+        <v>334</v>
+      </c>
+      <c r="K5" t="n">
         <v>333</v>
       </c>
-      <c r="K5" t="n">
-        <v>332</v>
-      </c>
       <c r="L5" t="n">
-        <v>0.002650641137175391</v>
+        <v>0.002559813142906098</v>
       </c>
       <c r="M5" t="n">
-        <v>3.356050797083426</v>
+        <v>3.350149936524989</v>
       </c>
       <c r="N5" t="n">
-        <v>23.90572113184576</v>
+        <v>23.8379863070361</v>
       </c>
       <c r="O5" t="n">
-        <v>4.889347720488466</v>
+        <v>4.88241603174454</v>
       </c>
       <c r="P5" t="n">
-        <v>366.9355818644965</v>
+        <v>366.9426435478341</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -23395,28 +23462,28 @@
         <v>0.09660000000000001</v>
       </c>
       <c r="I6" t="n">
-        <v>0.06130135696240931</v>
+        <v>0.06200332012054075</v>
       </c>
       <c r="J6" t="n">
+        <v>334</v>
+      </c>
+      <c r="K6" t="n">
         <v>333</v>
       </c>
-      <c r="K6" t="n">
-        <v>332</v>
-      </c>
       <c r="L6" t="n">
-        <v>0.007700444019181907</v>
+        <v>0.007926654965514923</v>
       </c>
       <c r="M6" t="n">
-        <v>3.884347165631132</v>
+        <v>3.876500587926911</v>
       </c>
       <c r="N6" t="n">
-        <v>28.51202203502652</v>
+        <v>28.43082105572033</v>
       </c>
       <c r="O6" t="n">
-        <v>5.339664974043457</v>
+        <v>5.332055987676829</v>
       </c>
       <c r="P6" t="n">
-        <v>363.1193465396404</v>
+        <v>363.1119724998956</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -23473,28 +23540,28 @@
         <v>0.1426</v>
       </c>
       <c r="I7" t="n">
-        <v>0.07864754844866002</v>
+        <v>0.08090547456916714</v>
       </c>
       <c r="J7" t="n">
+        <v>334</v>
+      </c>
+      <c r="K7" t="n">
         <v>333</v>
       </c>
-      <c r="K7" t="n">
-        <v>332</v>
-      </c>
       <c r="L7" t="n">
-        <v>0.01605561218947249</v>
+        <v>0.01705031076010077</v>
       </c>
       <c r="M7" t="n">
-        <v>3.701418888313259</v>
+        <v>3.701202575460603</v>
       </c>
       <c r="N7" t="n">
-        <v>22.31900735396237</v>
+        <v>22.29772188963489</v>
       </c>
       <c r="O7" t="n">
-        <v>4.724299668094983</v>
+        <v>4.722046366739201</v>
       </c>
       <c r="P7" t="n">
-        <v>356.8445116681855</v>
+        <v>356.8207924220104</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -23551,28 +23618,28 @@
         <v>0.0623</v>
       </c>
       <c r="I8" t="n">
-        <v>0.09598178388925892</v>
+        <v>0.1003556407820946</v>
       </c>
       <c r="J8" t="n">
+        <v>334</v>
+      </c>
+      <c r="K8" t="n">
         <v>333</v>
       </c>
-      <c r="K8" t="n">
-        <v>332</v>
-      </c>
       <c r="L8" t="n">
-        <v>0.01742037777784944</v>
+        <v>0.01903115815316314</v>
       </c>
       <c r="M8" t="n">
-        <v>4.116985056475394</v>
+        <v>4.130737940557593</v>
       </c>
       <c r="N8" t="n">
-        <v>30.59487136123169</v>
+        <v>30.6746245446855</v>
       </c>
       <c r="O8" t="n">
-        <v>5.5312630891354</v>
+        <v>5.538467707289219</v>
       </c>
       <c r="P8" t="n">
-        <v>370.5641539447457</v>
+        <v>370.5182070966918</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -23629,28 +23696,28 @@
         <v>0.0648</v>
       </c>
       <c r="I9" t="n">
-        <v>0.1451910665676912</v>
+        <v>0.1472997178210938</v>
       </c>
       <c r="J9" t="n">
+        <v>334</v>
+      </c>
+      <c r="K9" t="n">
         <v>333</v>
       </c>
-      <c r="K9" t="n">
-        <v>332</v>
-      </c>
       <c r="L9" t="n">
-        <v>0.04353416373236219</v>
+        <v>0.0449693262122115</v>
       </c>
       <c r="M9" t="n">
-        <v>4.010390453454042</v>
+        <v>4.008170127363413</v>
       </c>
       <c r="N9" t="n">
-        <v>27.26966857230463</v>
+        <v>27.22766847657487</v>
       </c>
       <c r="O9" t="n">
-        <v>5.222036822189655</v>
+        <v>5.218013844038254</v>
       </c>
       <c r="P9" t="n">
-        <v>366.2215397073676</v>
+        <v>366.199388575972</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -23707,28 +23774,28 @@
         <v>0.08</v>
       </c>
       <c r="I10" t="n">
-        <v>0.1772826519433682</v>
+        <v>0.1800266142671313</v>
       </c>
       <c r="J10" t="n">
+        <v>334</v>
+      </c>
+      <c r="K10" t="n">
         <v>333</v>
       </c>
-      <c r="K10" t="n">
-        <v>332</v>
-      </c>
       <c r="L10" t="n">
-        <v>0.07466876495860064</v>
+        <v>0.0770758828732121</v>
       </c>
       <c r="M10" t="n">
-        <v>3.540013970654657</v>
+        <v>3.542771799451724</v>
       </c>
       <c r="N10" t="n">
-        <v>22.93250760261962</v>
+        <v>22.9311903071731</v>
       </c>
       <c r="O10" t="n">
-        <v>4.788789784759779</v>
+        <v>4.788652243290705</v>
       </c>
       <c r="P10" t="n">
-        <v>358.5012106977479</v>
+        <v>358.4723856988866</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -23785,28 +23852,28 @@
         <v>0.0946</v>
       </c>
       <c r="I11" t="n">
-        <v>0.2707562906857534</v>
+        <v>0.2723714499311113</v>
       </c>
       <c r="J11" t="n">
+        <v>334</v>
+      </c>
+      <c r="K11" t="n">
         <v>333</v>
       </c>
-      <c r="K11" t="n">
-        <v>332</v>
-      </c>
       <c r="L11" t="n">
-        <v>0.1380447046093334</v>
+        <v>0.1401509915975581</v>
       </c>
       <c r="M11" t="n">
-        <v>4.200666761853856</v>
+        <v>4.195520892939659</v>
       </c>
       <c r="N11" t="n">
-        <v>26.95149834315636</v>
+        <v>26.89396711989732</v>
       </c>
       <c r="O11" t="n">
-        <v>5.191483250782608</v>
+        <v>5.185939367163612</v>
       </c>
       <c r="P11" t="n">
-        <v>347.888733764586</v>
+        <v>347.8717667082219</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -23863,28 +23930,28 @@
         <v>0.0968</v>
       </c>
       <c r="I12" t="n">
-        <v>0.3181747550819841</v>
+        <v>0.3207699895441588</v>
       </c>
       <c r="J12" t="n">
+        <v>334</v>
+      </c>
+      <c r="K12" t="n">
         <v>333</v>
       </c>
-      <c r="K12" t="n">
-        <v>332</v>
-      </c>
       <c r="L12" t="n">
-        <v>0.1658762075858097</v>
+        <v>0.1687730134776614</v>
       </c>
       <c r="M12" t="n">
-        <v>4.375474761147429</v>
+        <v>4.373640554817142</v>
       </c>
       <c r="N12" t="n">
-        <v>29.97358301214519</v>
+        <v>29.94399722159983</v>
       </c>
       <c r="O12" t="n">
-        <v>5.474813513914897</v>
+        <v>5.472110856113921</v>
       </c>
       <c r="P12" t="n">
-        <v>347.0461620556675</v>
+        <v>347.0188994253576</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -23941,28 +24008,28 @@
         <v>0.1069</v>
       </c>
       <c r="I13" t="n">
-        <v>0.3129547949713758</v>
+        <v>0.315740485296527</v>
       </c>
       <c r="J13" t="n">
+        <v>334</v>
+      </c>
+      <c r="K13" t="n">
         <v>333</v>
       </c>
-      <c r="K13" t="n">
-        <v>332</v>
-      </c>
       <c r="L13" t="n">
-        <v>0.1852311334090985</v>
+        <v>0.1885039260936084</v>
       </c>
       <c r="M13" t="n">
-        <v>3.977742050437891</v>
+        <v>3.978895141465356</v>
       </c>
       <c r="N13" t="n">
-        <v>25.36556113935818</v>
+        <v>25.35900746419921</v>
       </c>
       <c r="O13" t="n">
-        <v>5.036423447185332</v>
+        <v>5.035772777260627</v>
       </c>
       <c r="P13" t="n">
-        <v>354.3810358197521</v>
+        <v>354.3517724731839</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -24019,28 +24086,28 @@
         <v>0.1045</v>
       </c>
       <c r="I14" t="n">
-        <v>0.2629213959738328</v>
+        <v>0.2656336591661931</v>
       </c>
       <c r="J14" t="n">
+        <v>334</v>
+      </c>
+      <c r="K14" t="n">
         <v>333</v>
       </c>
-      <c r="K14" t="n">
-        <v>332</v>
-      </c>
       <c r="L14" t="n">
-        <v>0.1499989776370163</v>
+        <v>0.1531138845192257</v>
       </c>
       <c r="M14" t="n">
-        <v>3.664952894901113</v>
+        <v>3.66677052500194</v>
       </c>
       <c r="N14" t="n">
-        <v>23.06448812781466</v>
+        <v>23.06122281177183</v>
       </c>
       <c r="O14" t="n">
-        <v>4.802550169213712</v>
+        <v>4.802210200706736</v>
       </c>
       <c r="P14" t="n">
-        <v>362.3862662147735</v>
+        <v>362.357774211529</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -24097,28 +24164,28 @@
         <v>0.07290000000000001</v>
       </c>
       <c r="I15" t="n">
-        <v>0.1909591781130116</v>
+        <v>0.194557309883083</v>
       </c>
       <c r="J15" t="n">
+        <v>334</v>
+      </c>
+      <c r="K15" t="n">
         <v>333</v>
       </c>
-      <c r="K15" t="n">
-        <v>332</v>
-      </c>
       <c r="L15" t="n">
-        <v>0.07039059311781815</v>
+        <v>0.07303979779675729</v>
       </c>
       <c r="M15" t="n">
-        <v>4.088727817755822</v>
+        <v>4.093907984110426</v>
       </c>
       <c r="N15" t="n">
-        <v>28.35487724197559</v>
+        <v>28.38587696641335</v>
       </c>
       <c r="O15" t="n">
-        <v>5.324929787516037</v>
+        <v>5.327839802998335</v>
       </c>
       <c r="P15" t="n">
-        <v>361.9018271552758</v>
+        <v>361.8640292076594</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -24175,28 +24242,28 @@
         <v>0.2</v>
       </c>
       <c r="I16" t="n">
-        <v>1.207673789430289</v>
+        <v>1.21331843704719</v>
       </c>
       <c r="J16" t="n">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="K16" t="n">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="L16" t="n">
-        <v>0.3681969078083659</v>
+        <v>0.3714423461704883</v>
       </c>
       <c r="M16" t="n">
-        <v>9.722138826710122</v>
+        <v>9.72849628827159</v>
       </c>
       <c r="N16" t="n">
-        <v>148.0544229237079</v>
+        <v>147.8950487024923</v>
       </c>
       <c r="O16" t="n">
-        <v>12.16776162339269</v>
+        <v>12.16121082386505</v>
       </c>
       <c r="P16" t="n">
-        <v>346.7533696716071</v>
+        <v>346.6941466101089</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -24234,7 +24301,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q334"/>
+  <dimension ref="A1:Q335"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -53239,6 +53306,93 @@
         </is>
       </c>
     </row>
+    <row r="335">
+      <c r="A335" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-05 22:06:04+00:00</t>
+        </is>
+      </c>
+      <c r="B335" t="inlineStr">
+        <is>
+          <t>-38.123926113576864,174.73341404361443</t>
+        </is>
+      </c>
+      <c r="C335" t="inlineStr">
+        <is>
+          <t>-38.123637443202654,174.73424038979744</t>
+        </is>
+      </c>
+      <c r="D335" t="inlineStr">
+        <is>
+          <t>-38.123257949508435,174.7349980984407</t>
+        </is>
+      </c>
+      <c r="E335" t="inlineStr">
+        <is>
+          <t>-38.122842041001164,174.73567195915743</t>
+        </is>
+      </c>
+      <c r="F335" t="inlineStr">
+        <is>
+          <t>-38.12236104719708,174.7363267977118</t>
+        </is>
+      </c>
+      <c r="G335" t="inlineStr">
+        <is>
+          <t>-38.12189426024393,174.73700277530457</t>
+        </is>
+      </c>
+      <c r="H335" t="inlineStr">
+        <is>
+          <t>-38.12129269174179,174.73751281860115</t>
+        </is>
+      </c>
+      <c r="I335" t="inlineStr">
+        <is>
+          <t>-38.12085170897121,174.73822044304833</t>
+        </is>
+      </c>
+      <c r="J335" t="inlineStr">
+        <is>
+          <t>-38.12040226788232,174.73891926032303</t>
+        </is>
+      </c>
+      <c r="K335" t="inlineStr">
+        <is>
+          <t>-38.11999171907194,174.73966224113238</t>
+        </is>
+      </c>
+      <c r="L335" t="inlineStr">
+        <is>
+          <t>-38.11951186844983,174.7403219669247</t>
+        </is>
+      </c>
+      <c r="M335" t="inlineStr">
+        <is>
+          <t>-38.11899851123757,174.74093809356148</t>
+        </is>
+      </c>
+      <c r="N335" t="inlineStr">
+        <is>
+          <t>-38.11846520203089,174.74151165414742</t>
+        </is>
+      </c>
+      <c r="O335" t="inlineStr">
+        <is>
+          <t>-38.11794217312404,174.74210631708468</t>
+        </is>
+      </c>
+      <c r="P335" t="inlineStr">
+        <is>
+          <t>-38.11731696371281,174.74255897824276</t>
+        </is>
+      </c>
+      <c r="Q335" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
